--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N35_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.733734521635557</v>
+        <v>0.9317318597657781</v>
       </c>
       <c r="D2" t="n">
-        <v>6.212934539990657</v>
+        <v>1.009601862748482</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
